--- a/MAJSushiConfig/ig/StructureDefinition-FRLMMedicationUse.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMMedicationUse.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicationUse</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationUse</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMEntry|0.1.0</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -266,7 +266,7 @@
     <t>FRLMMedicationUse.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
 </t>
   </si>
   <si>
@@ -304,7 +304,7 @@
     <t>FRLMMedicationUse.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
 </t>
   </si>
   <si>
@@ -317,7 +317,7 @@
     <t>FRLMMedicationUse.header.author[x].authorOrganisation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation
 </t>
   </si>
   <si>
@@ -330,7 +330,7 @@
     <t>FRLMMedicationUse.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice
 </t>
   </si>
   <si>
@@ -343,8 +343,8 @@
     <t>FRLMMedicationUse.header.performer[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisation</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -392,7 +392,7 @@
     <t>FRLMMedicationUse.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMInformant
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMInformant
 </t>
   </si>
   <si>
@@ -466,7 +466,7 @@
     <t>FRLMMedicationUse.medication</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedication
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedication
 </t>
   </si>
   <si>
@@ -486,7 +486,7 @@
     <t>FRLMMedicationUse.dosageInstructions</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDosageInstructions
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDosageInstructions
 </t>
   </si>
   <si>
@@ -506,8 +506,8 @@
     <t>FRLMMedicationUse.derivedFrom[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPrescriptionItem
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicationDispensehttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicationAdministration</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPrescriptionItem
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationDispensehttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationAdministration</t>
   </si>
   <si>
     <t>Prescriptions, délivrances ou administrations à l'origine de cette déclaration d'utilisation du médicament.</t>
@@ -835,7 +835,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="163.8984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="152.51171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMMedicationUse.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMMedicationUse.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
